--- a/output/laminas_comunales/comunal_s_isapre_a_2024_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2024_valparaiso.xlsx
@@ -375,241 +375,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C2">
-        <v>54661</v>
+        <v>29.39862357222643</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C3">
-        <v>24223</v>
+        <v>20.65873632614024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="C4">
-        <v>18441</v>
+        <v>18.18342307352811</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C5">
-        <v>16318</v>
+        <v>15.83431342444801</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C6">
-        <v>13401</v>
+        <v>15.47526403557532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C7">
-        <v>8294</v>
+        <v>14.92098493201029</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="C8">
-        <v>8186</v>
+        <v>14.7608024691358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C9">
-        <v>6042</v>
+        <v>11.73384553637979</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C10">
-        <v>5231</v>
+        <v>11.12305463382717</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C11">
-        <v>4410</v>
+        <v>10.85562913907285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C12">
-        <v>4176</v>
+        <v>9.713966772014265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C13">
-        <v>3456</v>
+        <v>9.320583200519449</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C14">
-        <v>3248</v>
+        <v>8.403329973494605</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C15">
-        <v>2854</v>
+        <v>8.264653068741655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C16">
-        <v>2672</v>
+        <v>8.093523424768485</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C17">
-        <v>2380</v>
+        <v>8.083363450186724</v>
       </c>
     </row>
     <row r="18">
@@ -624,112 +624,112 @@
         </is>
       </c>
       <c r="C18">
-        <v>2330</v>
+        <v>8.021758589823039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C19">
-        <v>2251</v>
+        <v>7.978931904198796</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="C20">
-        <v>2060</v>
+        <v>7.939384935373645</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C21">
-        <v>1913</v>
+        <v>7.69203934975232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="C22">
-        <v>1882</v>
+        <v>7.565447121927788</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C23">
-        <v>1795</v>
+        <v>7.547070023270574</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C24">
-        <v>1729</v>
+        <v>7.367034896481089</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C25">
-        <v>1579</v>
+        <v>7.181723779854621</v>
       </c>
     </row>
     <row r="26">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>1483</v>
+        <v>6.488733318748633</v>
       </c>
     </row>
     <row r="27">
@@ -759,82 +759,82 @@
         </is>
       </c>
       <c r="C27">
-        <v>1358</v>
+        <v>6.261527111766876</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C28">
-        <v>1166</v>
+        <v>5.391271275078444</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="C29">
-        <v>1036</v>
+        <v>5.082824760244115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C30">
-        <v>945</v>
+        <v>5.069142286783018</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C31">
-        <v>835</v>
+        <v>4.628512710539249</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C32">
-        <v>740</v>
+        <v>4.473496553363442</v>
       </c>
     </row>
     <row r="33">
@@ -849,82 +849,82 @@
         </is>
       </c>
       <c r="C33">
-        <v>736</v>
+        <v>4.444712844978562</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="C34">
-        <v>671</v>
+        <v>4.105665181413113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C35">
-        <v>645</v>
+        <v>3.879219962256238</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C36">
-        <v>567</v>
+        <v>2.977782532719946</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="C37">
-        <v>254</v>
+        <v>2.712826333711691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="C38">
-        <v>239</v>
+        <v>2.524098181456822</v>
       </c>
     </row>
     <row r="39">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>0.779510022271715</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +995,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
